--- a/data/trans_orig/IP1012-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Provincia-trans_orig.xlsx
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6890</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102449</t>
+          <t>102245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108116</t>
+          <t>108115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203429</t>
+          <t>203562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38192</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>82825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>125098</t>
+          <t>124239</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130446</t>
+          <t>130467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>135655</t>
+          <t>135012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258002</t>
+          <t>258267</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263627</t>
+          <t>263629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>154739</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160582</t>
+          <t>160538</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317885</t>
+          <t>317889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14199</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>675700</t>
+          <t>675622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>680392</t>
+          <t>680386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>711942</t>
+          <t>711744</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>720101</t>
+          <t>720083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1389522</t>
+          <t>1390145</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1399628</t>
+          <t>1399743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48031</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56541</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108192</t>
+          <t>107825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113915</t>
+          <t>113921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74387</t>
+          <t>74413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>78125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155495</t>
+          <t>155384</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>84607</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52357</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110546</t>
+          <t>109906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138519</t>
+          <t>138021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145119</t>
+          <t>145112</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276826</t>
+          <t>276814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283833</t>
+          <t>283835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167401</t>
+          <t>168031</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332772</t>
+          <t>333398</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11670</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>699257</t>
+          <t>698681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>706010</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>737279</t>
+          <t>737697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>746262</t>
+          <t>746164</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1439472</t>
+          <t>1440256</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1450822</t>
+          <t>1450871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86308</t>
+          <t>86156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138501</t>
+          <t>138519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143426</t>
+          <t>144072</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>275774</t>
+          <t>275874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280809</t>
+          <t>280803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>738013</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744135</t>
+          <t>744121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1442369</t>
+          <t>1442258</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448501</t>
+          <t>1448505</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1012-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1012-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2374</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2374</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2374</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106383</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>102780</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108119</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,5%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>106383</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>102245</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>203562</t>
+          <t>203848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>209677</t>
+          <t>209676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150554</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3240</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41210</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>38320</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38612</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,26%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>124</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82825</t>
+          <t>83862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5290</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4383</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3643</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5188</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133713</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>130365</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135013</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>127889</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>124239</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>124979</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,43%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,17%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133713</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>130467</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135012</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>379</t>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258267</t>
+          <t>258086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3128,102 +3128,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3049</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4826</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4073</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>163358</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160424</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157270</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154739</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154855</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>163358</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>160538</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>492</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317889</t>
+          <t>317136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10822</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5643</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2617</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>10956</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>717011</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>711878</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>720202</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679012</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>675622</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>680386</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>675378</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>680387</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>717011</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>711744</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>720083</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2093</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1390145</t>
+          <t>1390657</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1399743</t>
+          <t>1399781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,72 +4045,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4870</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5495</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4582</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60142</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61568</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52038</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48400</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47469</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,63%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60142</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>56986</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61568</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>162</t>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107825</t>
+          <t>107679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113921</t>
+          <t>113912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>61568</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>61568</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>61568</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>61568</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>61568</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>61568</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5079,102 +5079,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3215</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3348</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4109</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4611</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5187,74 +5187,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81600</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>79019</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77105</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74413</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>74430</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81600</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78125</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>224</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155384</t>
+          <t>155601</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5417,107 +5417,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3698</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3795</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5399</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -5530,74 +5530,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43155</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>40203</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>40106</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>121</t>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84607</t>
+          <t>86316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5765,102 +5765,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4496</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,64%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1603</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1603</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -5873,74 +5873,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55070</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>51489</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>50902</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,36%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>160</t>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109906</t>
+          <t>111082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,92 +6103,92 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>2673</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7718</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2673</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6216,72 +6216,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>143066</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>137178</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145112</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>143066</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>138021</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145112</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276814</t>
+          <t>276485</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283835</t>
+          <t>283829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>652</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3284</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3308</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6559,72 +6559,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170663</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167097</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170663</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>168031</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333398</t>
+          <t>332715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11838</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>8247</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>7739</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,13%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2785</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>11252</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742877</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>737111</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>746228</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1014</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>703685</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698681</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>706006</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>699189</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>706005</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>99,87%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742877</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>737697</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>746164</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2073</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1440256</t>
+          <t>1439551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1450871</t>
+          <t>1450743</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748949</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748949</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8054,72 +8054,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8167,72 +8167,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8740,107 +8740,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3084</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3632</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8853,72 +8853,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45732</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43638</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45732</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>43266</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86156</t>
+          <t>86643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,92 +9426,92 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>2118</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5553</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -9539,72 +9539,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>141954</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>138337</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>143429</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>141954</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>138519</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>275874</t>
+          <t>275846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280803</t>
+          <t>280809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,92 +10112,92 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6647</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>2736</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>712</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -10225,74 +10225,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742108</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>738197</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744133</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,63%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742108</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>738013</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744121</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2121</t>
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1442258</t>
+          <t>1442525</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448505</t>
+          <t>1448503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
